--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1545,6 +1545,670 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122729372</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103771</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörabacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568380</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6274580</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>20 plantor på ca 50 m2</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122729676</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100530</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörabacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568560</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6274580</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122729097</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100530</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörabacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568380</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6274580</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Här och var inom den öppna gläntan.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122729481</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90857</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörabacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568440</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6274570</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122729578</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100510</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörabacken, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568440</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6274650</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Rullstensås mot norr</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729676</v>
+        <v>122729578</v>
       </c>
       <c r="B9" t="n">
-        <v>100633</v>
+        <v>100621</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,36 +1559,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1599,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R9" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,11 +1633,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1659,7 +1650,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1677,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729481</v>
+        <v>122729372</v>
       </c>
       <c r="B10" t="n">
-        <v>90960</v>
+        <v>103882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,34 +1684,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>224416</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1728,13 +1720,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R10" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1768,7 +1760,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,26 +1783,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1822,18 +1794,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729578</v>
+        <v>122729481</v>
       </c>
       <c r="B11" t="n">
-        <v>100613</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,35 +1810,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1881,10 +1852,10 @@
         <v>568440</v>
       </c>
       <c r="R11" t="n">
-        <v>6274650</v>
+        <v>6274570</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1914,6 +1885,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,7 +1909,27 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1947,14 +1943,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729372</v>
+        <v>122729097</v>
       </c>
       <c r="B12" t="n">
-        <v>103874</v>
+        <v>100641</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224416</v>
+        <v>224913</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729097</v>
+        <v>122729676</v>
       </c>
       <c r="B13" t="n">
-        <v>100633</v>
+        <v>100641</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568380</v>
+        <v>568560</v>
       </c>
       <c r="R13" t="n">
         <v>6274580</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1668,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B10" t="n">
-        <v>103882</v>
+        <v>90964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,35 +1684,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1720,13 +1719,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R10" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1760,7 +1759,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,6 +1782,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1794,14 +1813,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729481</v>
+        <v>122729097</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>100641</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,38 +1833,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,13 +1873,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R11" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1889,7 +1913,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,26 +1936,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1943,15 +1947,11 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729097</v>
+        <v>122729676</v>
       </c>
       <c r="B12" t="n">
         <v>100641</v>
@@ -1982,7 +1982,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568380</v>
+        <v>568560</v>
       </c>
       <c r="R12" t="n">
         <v>6274580</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729676</v>
+        <v>122729372</v>
       </c>
       <c r="B13" t="n">
-        <v>100641</v>
+        <v>103882</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,26 +2093,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568560</v>
+        <v>568380</v>
       </c>
       <c r="R13" t="n">
         <v>6274580</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729578</v>
+        <v>122729097</v>
       </c>
       <c r="B9" t="n">
-        <v>100621</v>
+        <v>100643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,32 +1559,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1595,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R9" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,6 +1637,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Här och var inom den öppna gläntan.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1659,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1668,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729481</v>
+        <v>122729372</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>103884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,34 +1693,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>224416</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1719,13 +1729,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R10" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1769,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,26 +1792,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1813,18 +1803,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729097</v>
+        <v>122729676</v>
       </c>
       <c r="B11" t="n">
-        <v>100641</v>
+        <v>100643</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,7 +1838,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1873,7 +1859,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568380</v>
+        <v>568560</v>
       </c>
       <c r="R11" t="n">
         <v>6274580</v>
@@ -1913,7 +1899,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729676</v>
+        <v>122729481</v>
       </c>
       <c r="B12" t="n">
-        <v>100641</v>
+        <v>90964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,39 +1949,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224913</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2003,13 +1988,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2043,7 +2028,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,6 +2051,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
@@ -2077,14 +2082,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729372</v>
+        <v>122729578</v>
       </c>
       <c r="B13" t="n">
-        <v>103882</v>
+        <v>100623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,33 +2102,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224416</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2133,10 +2138,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R13" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,11 +2176,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>20 plantor på ca 50 m2</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729097</v>
+        <v>122729578</v>
       </c>
       <c r="B9" t="n">
-        <v>100643</v>
+        <v>100623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,36 +1559,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1599,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R9" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,11 +1633,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Här och var inom den öppna gläntan.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1659,7 +1650,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1677,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B10" t="n">
-        <v>103884</v>
+        <v>90964</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,35 +1684,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1729,13 +1719,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R10" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1769,7 +1759,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,6 +1782,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1803,11 +1813,15 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729676</v>
+        <v>122729097</v>
       </c>
       <c r="B11" t="n">
         <v>100643</v>
@@ -1838,7 +1852,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1859,7 +1873,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568560</v>
+        <v>568380</v>
       </c>
       <c r="R11" t="n">
         <v>6274580</v>
@@ -1899,7 +1913,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1937,10 +1951,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729481</v>
+        <v>122729676</v>
       </c>
       <c r="B12" t="n">
-        <v>90964</v>
+        <v>100643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1949,38 +1963,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1988,13 +2003,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R12" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2028,7 +2043,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,26 +2066,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
@@ -2082,18 +2077,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729578</v>
+        <v>122729372</v>
       </c>
       <c r="B13" t="n">
-        <v>100623</v>
+        <v>103884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2102,29 +2093,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224416</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2138,10 +2133,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R13" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,6 +2171,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>20 plantor på ca 50 m2</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1550,7 +1550,7 @@
         <v>122729578</v>
       </c>
       <c r="B9" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>122729481</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729097</v>
+        <v>122729372</v>
       </c>
       <c r="B11" t="n">
-        <v>100643</v>
+        <v>103892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,26 +1833,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1954,7 +1954,7 @@
         <v>122729676</v>
       </c>
       <c r="B12" t="n">
-        <v>100643</v>
+        <v>100651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729372</v>
+        <v>122729097</v>
       </c>
       <c r="B13" t="n">
-        <v>103884</v>
+        <v>100651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,26 +2093,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224416</v>
+        <v>224913</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729578</v>
+        <v>122729097</v>
       </c>
       <c r="B9" t="n">
-        <v>100631</v>
+        <v>100651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,32 +1559,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1595,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R9" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,6 +1637,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Här och var inom den öppna gläntan.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1659,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1668,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729481</v>
+        <v>122729676</v>
       </c>
       <c r="B10" t="n">
-        <v>90972</v>
+        <v>100651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,38 +1689,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1719,13 +1729,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R10" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1769,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,26 +1792,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1813,18 +1803,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B11" t="n">
-        <v>103892</v>
+        <v>90972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1837,35 +1823,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1873,13 +1858,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R11" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1913,7 +1898,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1936,6 +1921,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1947,14 +1952,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729676</v>
+        <v>122729578</v>
       </c>
       <c r="B12" t="n">
-        <v>100651</v>
+        <v>100631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,36 +1972,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2003,10 +2008,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2041,11 +2046,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729097</v>
+        <v>122729372</v>
       </c>
       <c r="B13" t="n">
-        <v>100651</v>
+        <v>103892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,26 +2093,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729097</v>
+        <v>122729676</v>
       </c>
       <c r="B9" t="n">
         <v>100651</v>
@@ -1578,7 +1578,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568380</v>
+        <v>568560</v>
       </c>
       <c r="R9" t="n">
         <v>6274580</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729676</v>
+        <v>122729578</v>
       </c>
       <c r="B10" t="n">
-        <v>100651</v>
+        <v>100631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,36 +1689,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1729,10 +1725,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R10" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1767,11 +1763,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1789,7 +1780,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1960,10 +1951,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729578</v>
+        <v>122729097</v>
       </c>
       <c r="B12" t="n">
-        <v>100631</v>
+        <v>100651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1972,32 +1963,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2008,10 +2003,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R12" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,6 +2041,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Här och var inom den öppna gläntan.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729676</v>
+        <v>122729372</v>
       </c>
       <c r="B9" t="n">
-        <v>100651</v>
+        <v>103892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,26 +1559,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568560</v>
+        <v>568380</v>
       </c>
       <c r="R9" t="n">
         <v>6274580</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729578</v>
+        <v>122729097</v>
       </c>
       <c r="B10" t="n">
-        <v>100631</v>
+        <v>100651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,32 +1689,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1725,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R10" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,6 +1767,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Här och var inom den öppna gläntan.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1780,7 +1789,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1798,10 +1807,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729481</v>
+        <v>122729676</v>
       </c>
       <c r="B11" t="n">
-        <v>90972</v>
+        <v>100651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,38 +1819,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1849,13 +1859,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R11" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1889,7 +1899,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,26 +1922,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1943,18 +1933,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729097</v>
+        <v>122729578</v>
       </c>
       <c r="B12" t="n">
-        <v>100651</v>
+        <v>100631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1963,36 +1949,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2003,10 +1985,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2041,11 +2023,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Här och var inom den öppna gläntan.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2040,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B13" t="n">
-        <v>103892</v>
+        <v>90972</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,35 +2074,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2133,13 +2109,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R13" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2173,7 +2149,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2196,6 +2172,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2207,7 +2203,11 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1937,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729578</v>
+        <v>122729481</v>
       </c>
       <c r="B12" t="n">
-        <v>100631</v>
+        <v>90972</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1949,35 +1949,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1988,10 +1991,10 @@
         <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274650</v>
+        <v>6274570</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,6 +2024,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2040,7 +2048,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2054,14 +2082,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729481</v>
+        <v>122729578</v>
       </c>
       <c r="B13" t="n">
-        <v>90972</v>
+        <v>100631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,38 +2102,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2112,10 +2141,10 @@
         <v>568440</v>
       </c>
       <c r="R13" t="n">
-        <v>6274570</v>
+        <v>6274650</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2145,11 +2174,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,27 +2193,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2203,11 +2207,7 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B9" t="n">
-        <v>103892</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,35 +1563,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1599,13 +1598,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R9" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1639,7 +1638,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,6 +1661,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1673,14 +1692,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729097</v>
+        <v>122729372</v>
       </c>
       <c r="B10" t="n">
-        <v>100651</v>
+        <v>103895</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,26 +1712,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1718,7 +1741,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1769,7 +1792,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1807,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729676</v>
+        <v>122729097</v>
       </c>
       <c r="B11" t="n">
-        <v>100651</v>
+        <v>100654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1838,7 +1861,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1859,7 +1882,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568560</v>
+        <v>568380</v>
       </c>
       <c r="R11" t="n">
         <v>6274580</v>
@@ -1899,7 +1922,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1937,10 +1960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729481</v>
+        <v>122729578</v>
       </c>
       <c r="B12" t="n">
-        <v>90972</v>
+        <v>100634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1949,38 +1972,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1991,10 +2011,10 @@
         <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274570</v>
+        <v>6274650</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2024,11 +2044,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2048,27 +2063,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2082,18 +2077,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729578</v>
+        <v>122729676</v>
       </c>
       <c r="B13" t="n">
-        <v>100631</v>
+        <v>100654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2102,32 +2093,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2138,10 +2133,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R13" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,6 +2171,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -1547,10 +1547,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729481</v>
+        <v>122729097</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>100656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,38 +1559,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1598,13 +1599,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R9" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1638,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,26 +1662,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1692,18 +1673,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729372</v>
+        <v>122729481</v>
       </c>
       <c r="B10" t="n">
-        <v>103895</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,35 +1693,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1752,13 +1728,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R10" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1792,7 +1768,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1815,6 +1791,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1826,14 +1822,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729097</v>
+        <v>122729372</v>
       </c>
       <c r="B11" t="n">
-        <v>100654</v>
+        <v>103897</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,26 +1842,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,10 +1960,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729578</v>
+        <v>122729676</v>
       </c>
       <c r="B12" t="n">
-        <v>100634</v>
+        <v>100656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1972,32 +1972,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2008,10 +2012,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R12" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,6 +2050,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2063,7 +2072,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2081,10 +2090,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122729676</v>
+        <v>122729578</v>
       </c>
       <c r="B13" t="n">
-        <v>100654</v>
+        <v>100636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2093,36 +2102,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2133,10 +2138,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R13" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2171,11 +2176,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116181426</v>
+        <v>122729097</v>
       </c>
       <c r="B8" t="n">
-        <v>100014</v>
+        <v>100656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1461,19 +1461,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörabacken, mellan Södra Ölvingstorp och Fureborg, Sm</t>
+          <t>Mörabacken, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568385</v>
+        <v>568380</v>
       </c>
       <c r="R8" t="n">
-        <v>6274585</v>
+        <v>6274580</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,24 +1502,19 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Hf-Kal-1842</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ungefärligt antal då i princip alla blomstänglar var avbetade eller avklippta!</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,29 +1527,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Rullstensås</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Ålind</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Ålind</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729097</v>
+        <v>122729481</v>
       </c>
       <c r="B9" t="n">
-        <v>100656</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,39 +1564,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>224913</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1599,13 +1603,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568380</v>
+        <v>568440</v>
       </c>
       <c r="R9" t="n">
-        <v>6274580</v>
+        <v>6274570</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1639,7 +1643,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,6 +1666,26 @@
           <t>Rullstensås</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1673,14 +1697,18 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729481</v>
+        <v>122729372</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>103897</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,34 +1721,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>224416</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1728,13 +1757,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568440</v>
+        <v>568380</v>
       </c>
       <c r="R10" t="n">
-        <v>6274570</v>
+        <v>6274580</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1768,7 +1797,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,26 +1820,6 @@
           <t>Rullstensås</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1822,18 +1831,14 @@
           <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729372</v>
+        <v>122729676</v>
       </c>
       <c r="B11" t="n">
-        <v>103897</v>
+        <v>100656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,26 +1847,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224416</v>
+        <v>224913</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1871,7 +1876,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1882,7 +1887,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568380</v>
+        <v>568560</v>
       </c>
       <c r="R11" t="n">
         <v>6274580</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,10 +1965,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729676</v>
+        <v>122729578</v>
       </c>
       <c r="B12" t="n">
-        <v>100656</v>
+        <v>100636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1972,36 +1977,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224913</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2012,10 +2013,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568560</v>
+        <v>568440</v>
       </c>
       <c r="R12" t="n">
-        <v>6274580</v>
+        <v>6274650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2050,11 +2051,6 @@
           <t>2024-10-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2068,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,127 +2083,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>122729578</v>
-      </c>
-      <c r="B13" t="n">
-        <v>100636</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Mörabacken, Sm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>568440</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6274650</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Torr gräsmark med tall</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Rullstensås mot norr</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Ekologa /Jonas Wäglind</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Ekologa /Jonas Wäglind</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,12 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568566.9328486499</v>
+        <v>568567</v>
       </c>
       <c r="R3" t="n">
-        <v>6274586.745796213</v>
+        <v>6274587</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -875,19 +870,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,12 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568467.1286955005</v>
+        <v>568467</v>
       </c>
       <c r="R4" t="n">
-        <v>6274585.672437535</v>
+        <v>6274586</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,19 +981,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1057,12 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568566.9328486499</v>
+        <v>568567</v>
       </c>
       <c r="R5" t="n">
-        <v>6274586.745796213</v>
+        <v>6274587</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1127,19 +1092,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1183,12 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>98537</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568566.9328486499</v>
+        <v>568567</v>
       </c>
       <c r="R6" t="n">
-        <v>6274586.745796213</v>
+        <v>6274587</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1253,19 +1203,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100251</v>
+        <v>100257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100791</v>
+        <v>100797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>100258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100797</v>
+        <v>100798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110507</v>
+        <v>110535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100258</v>
+        <v>100285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100798</v>
+        <v>100825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110535</v>
+        <v>110541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100285</v>
+        <v>100291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100825</v>
+        <v>100831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110541</v>
+        <v>110548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100291</v>
+        <v>100298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100831</v>
+        <v>100838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110548</v>
+        <v>110552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100298</v>
+        <v>100302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100838</v>
+        <v>100842</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110552</v>
+        <v>110560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100302</v>
+        <v>100309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100842</v>
+        <v>100849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110563</v>
+        <v>110568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100312</v>
+        <v>100317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98683</v>
+        <v>98688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100852</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110568</v>
+        <v>110576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100317</v>
+        <v>100325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98688</v>
+        <v>98696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>100865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>74723995</v>
       </c>
       <c r="B4" t="n">
-        <v>100325</v>
+        <v>100335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74768897</v>
       </c>
       <c r="B5" t="n">
-        <v>98696</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>74858240</v>
       </c>
       <c r="B6" t="n">
-        <v>100865</v>
+        <v>100875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -675,58 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6307261</v>
+        <v>122729481</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörabacken (mellan S. Ölvingstorp och Fureborg), Sm</t>
+          <t>Mörabacken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568384.9678991842</v>
+        <v>568440</v>
       </c>
       <c r="R2" t="n">
-        <v>6274584.887897454</v>
+        <v>6274570</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-05-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Funnen 1985, lokalen då kallad S. Ölvingstorp 550 m S. Koordinaten avser det största beståndet. Fläckvis förekomst längs 350 m av kullens södra kant.</t>
+          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,33 +770,63 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ohävdad åskulle</t>
+          <t>Rullstensås</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Äldre tall</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Äldre tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Burén</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Burén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>74471136</v>
       </c>
       <c r="B3" t="n">
-        <v>110586</v>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,45 +934,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74723995</v>
+        <v>74768897</v>
       </c>
       <c r="B4" t="n">
-        <v>100335</v>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222617</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S. Ölvingstorp 600 m S, Sm</t>
+          <t>65 Ölvingstorp norra gdn 700 m S, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568467</v>
+        <v>568567</v>
       </c>
       <c r="R4" t="n">
-        <v>6274586</v>
+        <v>6274587</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -983,12 +1004,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>1986-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G5d 0940. SOM: Phleum phleoides. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4G5d 0941. SOM: Platanthera chlorantha. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1023,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Nu obetad, sydvänd åssluttning</t>
+          <t>Obetad åssluttning</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74768897</v>
+        <v>122729578</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,37 +1056,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>65 Ölvingstorp norra gdn 700 m S, Sm</t>
+          <t>Mörabacken, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568567</v>
+        <v>568440</v>
       </c>
       <c r="R5" t="n">
-        <v>6274587</v>
+        <v>6274650</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,17 +1118,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 4G5d 0941. SOM: Platanthera chlorantha. LEG: Thomas Karlsson</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,72 +1132,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Torr gräsmark med tall</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Obetad åssluttning</t>
+          <t>Rullstensås mot norr</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74858240</v>
+        <v>74723995</v>
       </c>
       <c r="B6" t="n">
-        <v>100875</v>
+        <v>100797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222886</v>
+        <v>222617</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S. Ölvingstorp 550 m S, Sm</t>
+          <t>S. Ölvingstorp 600 m S, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568567</v>
+        <v>568467</v>
       </c>
       <c r="R6" t="n">
-        <v>6274587</v>
+        <v>6274586</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1210,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G5d 0941. SOM: Pulsatilla vulgaris. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4G5d 0940. SOM: Phleum phleoides. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,7 +1250,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Åskulle</t>
+          <t>Nu obetad, sydvänd åssluttning</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1246,15 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116194896</v>
+        <v>74858240</v>
       </c>
       <c r="B7" t="n">
-        <v>100014</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,45 +1283,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224913</v>
+        <v>222886</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörabacken öst, Sm</t>
+          <t>S. Ölvingstorp 550 m S, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568728</v>
+        <v>568567</v>
       </c>
       <c r="R7" t="n">
-        <v>6274548</v>
+        <v>6274587</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,17 +1337,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Östliga delen av floraväktarlokal Mörabacken, cirka 200 meter från originallokalens koordinater</t>
+          <t>Smålands flora 2007: KOO: 4G5d 0941. SOM: Pulsatilla vulgaris. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,57 +1356,60 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Åskulle</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Ålind</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Ålind</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122729097</v>
+        <v>122729372</v>
       </c>
       <c r="B8" t="n">
-        <v>100656</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>224913</v>
+        <v>224416</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1403,7 +1419,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1454,7 +1470,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Här och var inom den öppna gläntan.</t>
+          <t>20 plantor på ca 50 m2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,64 +1508,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122729481</v>
+        <v>6280264</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>224913</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörabacken, Sm</t>
+          <t>Mörabacken, mellan Södra Ölvingstorp och Fureborg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568440</v>
+        <v>568385</v>
       </c>
       <c r="R9" t="n">
-        <v>6274570</v>
+        <v>6274585</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,19 +1567,19 @@
           <t>Ljungby</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Hf-Kal-1842</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växandes på en tall, 182 centimeter i omkrets eller 58 centimeter grov i diameter.</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,91 +1588,60 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Torr gräsmark med tall</t>
-        </is>
-      </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Rullstensås</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Äldre tall</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Äldre tall</t>
+          <t>Åskulle</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Thomas Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122729372</v>
+        <v>116194896</v>
       </c>
       <c r="B10" t="n">
-        <v>103897</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>224913</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1684,26 +1649,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörabacken, Sm</t>
+          <t>Mörabacken öst, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568380</v>
+        <v>568728</v>
       </c>
       <c r="R10" t="n">
-        <v>6274580</v>
+        <v>6274548</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,17 +1688,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>20 plantor på ca 50 m2</t>
+          <t>Östliga delen av floraväktarlokal Mörabacken, cirka 200 meter från originallokalens koordinater</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,40 +1711,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Torr gräsmark med tall</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Rullstensås</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Per Ålind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Per Ålind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122729676</v>
+        <v>122729097</v>
       </c>
       <c r="B11" t="n">
-        <v>100656</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1752,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1827,7 +1773,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568560</v>
+        <v>568380</v>
       </c>
       <c r="R11" t="n">
         <v>6274580</v>
@@ -1867,7 +1813,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+          <t>Här och var inom den öppna gläntan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,44 +1851,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122729578</v>
+        <v>122729676</v>
       </c>
       <c r="B12" t="n">
-        <v>100636</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>224913</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1953,10 +1898,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568440</v>
+        <v>568560</v>
       </c>
       <c r="R12" t="n">
-        <v>6274650</v>
+        <v>6274580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,6 +1936,11 @@
           <t>2024-10-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växandes fyra plantor, plus två plantor tillsammans, längs bruksvägen.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2008,7 +1958,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rullstensås mot norr</t>
+          <t>Rullstensås</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 4183-2024 artfynd.xlsx
+++ b/artfynd/A 4183-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -820,6 +825,11 @@
           <t>Inventering av skyddsvärda träd i kulturlandskapet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122729481</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74471136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74768897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1158,6 +1178,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122729578</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74723995</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,6 +1410,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74858240</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122729372</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6280264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116194896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122729097</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1973,8 +2028,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122729676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>